--- a/KNN.xlsx
+++ b/KNN.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejandrogarciaruiz/Desktop/DCI-AplicacionTecnologiaAvanzada/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E057567-02C8-CC4E-8592-340E92FD29C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F400216-7E90-CA42-8F08-73157813A398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="660" windowWidth="26240" windowHeight="14860" xr2:uid="{E727FED7-A702-6443-99DE-2A656021BEE2}"/>
+    <workbookView xWindow="15280" yWindow="12920" windowWidth="26240" windowHeight="14860" xr2:uid="{E727FED7-A702-6443-99DE-2A656021BEE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -500,11 +500,11 @@
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f ca="1">RANDBETWEEN(1, 50)</f>
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1">
         <f ca="1">RANDBETWEEN(1, 50)</f>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -522,7 +522,7 @@
         <v>7</v>
       </c>
       <c r="L2">
-        <f>SQRT(POWER(I$11-E2,2)+POWER(J$11-F2,2))</f>
+        <f t="shared" ref="L2:L7" si="0">SQRT(POWER(I$11-E2,2)+POWER(J$11-F2,2))</f>
         <v>34.205262752974143</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -540,12 +540,12 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:B18" ca="1" si="0">RANDBETWEEN(1, 50)</f>
-        <v>18</v>
+        <f t="shared" ref="A3:B18" ca="1" si="1">RANDBETWEEN(1, 50)</f>
+        <v>32</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <f>SQRT(POWER(I$11-E3,2)+POWER(J$11-F3,2))</f>
+        <f t="shared" si="0"/>
         <v>42.755116652863897</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -572,12 +572,12 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
@@ -599,7 +599,7 @@
         <v>5.4772255750516612</v>
       </c>
       <c r="L4">
-        <f>SQRT(POWER(I$11-E4,2)+POWER(J$11-F4,2))</f>
+        <f t="shared" si="0"/>
         <v>62.425956140054431</v>
       </c>
       <c r="N4" s="3" t="s">
@@ -611,12 +611,12 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>42</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -631,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="L5">
-        <f>SQRT(POWER(I$11-E5,2)+POWER(J$11-F5,2))</f>
+        <f t="shared" si="0"/>
         <v>17.464249196572979</v>
       </c>
       <c r="N5" s="3" t="s">
@@ -643,12 +643,12 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -663,7 +663,7 @@
         <v>2</v>
       </c>
       <c r="L6">
-        <f>SQRT(POWER(I$11-E6,2)+POWER(J$11-F6,2))</f>
+        <f t="shared" si="0"/>
         <v>48.020828814171878</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -675,12 +675,12 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
@@ -698,7 +698,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <f>SQRT(POWER(I$11-E7,2)+POWER(J$11-F7,2))</f>
+        <f t="shared" si="0"/>
         <v>37.054014627297811</v>
       </c>
       <c r="N7" s="1" t="s">
@@ -710,12 +710,12 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="L3:L31" si="1">SQRT(POWER(I$11-E8,2)+POWER(J$11-F8,2))</f>
+        <f t="shared" ref="L8:L31" si="2">SQRT(POWER(I$11-E8,2)+POWER(J$11-F8,2))</f>
         <v>58.180752831155424</v>
       </c>
       <c r="N8" s="1" t="s">
@@ -748,12 +748,12 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -774,7 +774,7 @@
         <v>-2</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.231546211727817</v>
       </c>
       <c r="N9" s="1" t="s">
@@ -786,12 +786,12 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2</v>
@@ -806,7 +806,7 @@
         <v>2</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>49.929950931279713</v>
       </c>
       <c r="N10" s="1" t="s">
@@ -818,11 +818,11 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>38</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -847,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="L11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>49.658836071740545</v>
       </c>
       <c r="N11" s="1" t="s">
@@ -860,11 +860,11 @@
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f ca="1">RANDBETWEEN(1, 50)*-1</f>
-        <v>-50</v>
+        <v>-31</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -879,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="L12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>47.010637094172637</v>
       </c>
       <c r="N12" s="1" t="s">
@@ -891,12 +891,12 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <f t="shared" ref="A13:B28" ca="1" si="2">RANDBETWEEN(1, 50)*-1</f>
-        <v>-18</v>
+        <f t="shared" ref="A13:B28" ca="1" si="3">RANDBETWEEN(1, 50)*-1</f>
+        <v>-12</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>39.66106403010388</v>
       </c>
       <c r="N13" s="1" t="s">
@@ -923,12 +923,12 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-45</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-5</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -943,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="L14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>50.47771785649585</v>
       </c>
       <c r="N14" s="1" t="s">
@@ -955,12 +955,12 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-45</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-7</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -975,7 +975,7 @@
         <v>3</v>
       </c>
       <c r="L15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>61.032778078668514</v>
       </c>
       <c r="N15" s="1" t="s">
@@ -987,12 +987,12 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-50</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-25</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1007,7 +1007,7 @@
         <v>3</v>
       </c>
       <c r="L16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>54.626001134990652</v>
       </c>
       <c r="N16" s="1" t="s">
@@ -1019,12 +1019,12 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-12</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1039,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="L17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>50.487622245457352</v>
       </c>
       <c r="N17" s="1" t="s">
@@ -1051,12 +1051,12 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-50</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-10</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1071,7 +1071,7 @@
         <v>3</v>
       </c>
       <c r="L18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30.463092423455635</v>
       </c>
       <c r="N18" s="1" t="s">
@@ -1083,12 +1083,12 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-39</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-20</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" ref="B19:B22" ca="1" si="3">RANDBETWEEN(1, 50)</f>
-        <v>45</v>
+        <f t="shared" ref="B19:B21" ca="1" si="4">RANDBETWEEN(1, 50)</f>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1103,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="L19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>60.307545133258408</v>
       </c>
       <c r="N19" s="1" t="s">
@@ -1115,12 +1115,12 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-11</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-41</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1135,7 +1135,7 @@
         <v>3</v>
       </c>
       <c r="L20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>42.80186911806539</v>
       </c>
       <c r="N20" s="1" t="s">
@@ -1147,12 +1147,12 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-16</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-10</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" ca="1" si="3"/>
-        <v>34</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>14</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1167,7 +1167,7 @@
         <v>3</v>
       </c>
       <c r="L21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31.622776601683793</v>
       </c>
       <c r="N21" s="1" t="s">
@@ -1179,12 +1179,12 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-26</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-15</v>
       </c>
       <c r="B22" s="1">
         <f ca="1">RANDBETWEEN(1, 50)*-1</f>
-        <v>-32</v>
+        <v>-20</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1199,7 +1199,7 @@
         <v>4</v>
       </c>
       <c r="L22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25.709920264364882</v>
       </c>
       <c r="N22" s="1" t="s">
@@ -1211,12 +1211,12 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-28</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-7</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-37</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-34</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1231,7 +1231,7 @@
         <v>4</v>
       </c>
       <c r="L23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35.902646142032481</v>
       </c>
       <c r="N23" s="1" t="s">
@@ -1243,12 +1243,12 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-16</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-8</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-14</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-10</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1263,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="L24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>53.814496188294839</v>
       </c>
       <c r="N24" s="1" t="s">
@@ -1275,12 +1275,12 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-44</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-38</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-27</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-1</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1295,7 +1295,7 @@
         <v>4</v>
       </c>
       <c r="L25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>62.968245965724662</v>
       </c>
       <c r="N25" s="1" t="s">
@@ -1307,12 +1307,12 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
+        <v>-4</v>
+      </c>
+      <c r="B26" s="1">
+        <f t="shared" ca="1" si="3"/>
         <v>-28</v>
-      </c>
-      <c r="B26" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-22</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1327,7 +1327,7 @@
         <v>4</v>
       </c>
       <c r="L26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>51.855568649856693</v>
       </c>
       <c r="N26" s="1" t="s">
@@ -1339,12 +1339,12 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-34</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-43</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-46</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-9</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1359,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="L27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>38.209946349085598</v>
       </c>
       <c r="N27" s="1" t="s">
@@ -1371,12 +1371,12 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-42</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-32</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-25</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>-36</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1391,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="L28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>49.203658400570177</v>
       </c>
       <c r="N28" s="1" t="s">
@@ -1403,12 +1403,12 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <f t="shared" ref="A29:B31" ca="1" si="4">RANDBETWEEN(1, 50)*-1</f>
-        <v>-3</v>
+        <f t="shared" ref="A29:B31" ca="1" si="5">RANDBETWEEN(1, 50)*-1</f>
+        <v>-41</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>-11</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-15</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1423,7 +1423,7 @@
         <v>4</v>
       </c>
       <c r="L29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23.021728866442675</v>
       </c>
       <c r="N29" s="1" t="s">
@@ -1435,12 +1435,12 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>-46</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-2</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>-23</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-30</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1455,7 +1455,7 @@
         <v>4</v>
       </c>
       <c r="L30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.0990195135927845</v>
       </c>
       <c r="N30" s="1" t="s">
@@ -1467,12 +1467,12 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>-27</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>-31</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-41</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1487,7 +1487,7 @@
         <v>4</v>
       </c>
       <c r="L31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>44.384682042344295</v>
       </c>
       <c r="N31" s="1" t="s">
@@ -1502,5 +1502,6 @@
     <sortCondition ref="O2:O31"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>